--- a/job_application_forms/041_expert_programmer_application_form--job_application_forms.xlsx
+++ b/job_application_forms/041_expert_programmer_application_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Date Of Birth Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date Decimal</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time Decimal</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>education_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Education 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>work_history</t>
+          <t>work_history_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Work History</t>
+          <t>Work History 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>resume_upload</t>
+          <t>resume_upload_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Resume Upload</t>
+          <t>Resume Upload 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'value1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'value1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'value2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'value2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'value1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'value1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1182,80 +1182,80 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'value2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'value2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>education_choices</t>
+          <t>education_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'value1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'value1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>education_choices</t>
+          <t>education_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>work_history_choices</t>
+          <t>work_history_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'value1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'value1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>work_history_choices</t>
+          <t>work_history_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
